--- a/docs/downloads/starr_omop_data_dictionary.xlsx
+++ b/docs/downloads/starr_omop_data_dictionary.xlsx
@@ -132,7 +132,7 @@
     <t>Source commit</t>
   </si>
   <si>
-    <t>9fb6445</t>
+    <t>f682f2b</t>
   </si>
   <si>
     <t>Source commit date</t>
